--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -68,6 +68,9 @@
     <t>SpreadAngle</t>
   </si>
   <si>
+    <t>Desc</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -89,6 +92,9 @@
     <t>#</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -128,19 +134,37 @@
     <t>散射角度(度)</t>
   </si>
   <si>
+    <t>武器描述</t>
+  </si>
+  <si>
     <t>霰弹枪1号</t>
   </si>
   <si>
+    <t>近距离散射，适合贴脸爆发</t>
+  </si>
+  <si>
     <t>步枪1号</t>
   </si>
   <si>
+    <t>高伤害单发，锁定追踪目标</t>
+  </si>
+  <si>
     <t>步枪2号</t>
   </si>
   <si>
+    <t>高射速连发，适合持续压制</t>
+  </si>
+  <si>
     <t>火箭炮1号</t>
   </si>
   <si>
+    <t>高爆发范围伤害，换弹较慢</t>
+  </si>
+  <si>
     <t>冲锋枪</t>
+  </si>
+  <si>
+    <t>可移动射击，机动性强</t>
   </si>
 </sst>
 </file>
@@ -618,161 +642,161 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -825,7 +849,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="29">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1016,28 +1040,182 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="19"/>
+      <tableStyleElement type="firstColumn" dxfId="20"/>
+      <tableStyleElement type="lastColumn" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="21"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="22"/>
+      <tableStyleElement type="totalRow" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="21"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="24"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="20"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="25"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="26"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="27"/>
+      <tableStyleElement type="pageFieldValues" dxfId="28"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1304,12 +1482,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.5" spans="1:13">
+    <row r="1" ht="28.5" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1349,289 +1527,321 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="84.75" s="2" customFormat="1">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="0">
+        <v>50009</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0">
+        <v>20</v>
+      </c>
+      <c r="F5" s="0">
+        <v>3</v>
+      </c>
+      <c r="G5" s="0">
+        <v>1500</v>
+      </c>
+      <c r="H5" s="0">
+        <v>4</v>
+      </c>
+      <c r="I5" s="0">
+        <v>3000</v>
+      </c>
+      <c r="J5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0">
+        <v>3</v>
+      </c>
+      <c r="L5" s="0">
+        <v>4</v>
+      </c>
+      <c r="M5" s="0">
+        <v>30</v>
+      </c>
+      <c r="N5" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0">
+        <v>50010</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="0">
+        <v>2</v>
+      </c>
+      <c r="E6" s="0">
+        <v>50</v>
+      </c>
+      <c r="F6" s="0">
+        <v>8</v>
+      </c>
+      <c r="G6" s="0">
+        <v>500</v>
+      </c>
+      <c r="H6" s="0">
+        <v>10</v>
+      </c>
+      <c r="I6" s="0">
+        <v>2000</v>
+      </c>
+      <c r="J6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0">
+        <v>1</v>
+      </c>
+      <c r="L6" s="0">
+        <v>1</v>
+      </c>
+      <c r="M6" s="0">
+        <v>0</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0">
+        <v>50011</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="0">
+        <v>3</v>
+      </c>
+      <c r="E7" s="0">
+        <v>10</v>
+      </c>
+      <c r="F7" s="0">
+        <v>15</v>
+      </c>
+      <c r="G7" s="0">
+        <v>400</v>
+      </c>
+      <c r="H7" s="0">
+        <v>20</v>
+      </c>
+      <c r="I7" s="0">
+        <v>2500</v>
+      </c>
+      <c r="J7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0">
+        <v>2</v>
+      </c>
+      <c r="L7" s="0">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0">
+        <v>0</v>
+      </c>
+      <c r="N7" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0">
+        <v>50012</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="0">
+        <v>4</v>
+      </c>
+      <c r="E8" s="0">
+        <v>100</v>
+      </c>
+      <c r="F8" s="0">
+        <v>20</v>
+      </c>
+      <c r="G8" s="0">
+        <v>3000</v>
+      </c>
+      <c r="H8" s="0">
+        <v>1</v>
+      </c>
+      <c r="I8" s="0">
+        <v>4000</v>
+      </c>
+      <c r="J8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0">
+        <v>3</v>
+      </c>
+      <c r="L8" s="0">
+        <v>1</v>
+      </c>
+      <c r="M8" s="0">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0">
+        <v>50013</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="0">
+        <v>5</v>
+      </c>
+      <c r="E9" s="0">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="84.75" spans="1:13">
-      <c r="A4" s="2" t="s">
+      <c r="F9" s="0">
+        <v>10</v>
+      </c>
+      <c r="G9" s="0">
+        <v>200</v>
+      </c>
+      <c r="H9" s="0">
+        <v>30</v>
+      </c>
+      <c r="I9" s="0">
+        <v>4000</v>
+      </c>
+      <c r="J9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="0">
+        <v>1</v>
+      </c>
+      <c r="L9" s="0">
+        <v>1</v>
+      </c>
+      <c r="M9" s="0">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="B5">
-        <v>50009</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1500</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>3000</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="B6">
-        <v>50010</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>50</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>500</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>2000</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="B7">
-        <v>50011</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>400</v>
-      </c>
-      <c r="H7">
-        <v>20</v>
-      </c>
-      <c r="I7">
-        <v>2500</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8">
-        <v>50012</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8">
-        <v>20</v>
-      </c>
-      <c r="G8">
-        <v>3000</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>4000</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>3</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="B9">
-        <v>50013</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>14</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>200</v>
-      </c>
-      <c r="H9">
-        <v>30</v>
-      </c>
-      <c r="I9">
-        <v>4000</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>20</v>
+      <c r="N9" s="0" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
@@ -1832,25 +1832,25 @@
         <v>77</v>
       </c>
       <c r="W5">
-        <v>-0.0045</v>
+        <v>-0.0042</v>
       </c>
       <c r="X5">
-        <v>-0.003</v>
+        <v>-0.0036</v>
       </c>
       <c r="Y5">
-        <v>-0.0024</v>
+        <v>-0.0015</v>
       </c>
       <c r="Z5">
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="AC5">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="AD5">
         <v>26</v>
@@ -1927,25 +1927,25 @@
         <v>77</v>
       </c>
       <c r="W6">
-        <v>-0.0045</v>
+        <v>-0.0042</v>
       </c>
       <c r="X6">
-        <v>-0.003</v>
+        <v>-0.0036</v>
       </c>
       <c r="Y6">
-        <v>-0.0024</v>
+        <v>-0.0015</v>
       </c>
       <c r="Z6">
         <v>6</v>
       </c>
       <c r="AA6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="AC6">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="AD6">
         <v>42</v>
@@ -2022,25 +2022,25 @@
         <v>77</v>
       </c>
       <c r="W7">
-        <v>-0.0045</v>
+        <v>-0.0042</v>
       </c>
       <c r="X7">
-        <v>-0.003</v>
+        <v>-0.0036</v>
       </c>
       <c r="Y7">
-        <v>-0.0024</v>
+        <v>-0.0015</v>
       </c>
       <c r="Z7">
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="AC7">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="AD7">
         <v>56</v>
@@ -2117,25 +2117,25 @@
         <v>77</v>
       </c>
       <c r="W8">
-        <v>-0.0045</v>
+        <v>-0.0042</v>
       </c>
       <c r="X8">
-        <v>-0.003</v>
+        <v>-0.0036</v>
       </c>
       <c r="Y8">
-        <v>-0.0024</v>
+        <v>-0.0015</v>
       </c>
       <c r="Z8">
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="AC8">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="AD8">
         <v>24</v>
@@ -2212,25 +2212,25 @@
         <v>77</v>
       </c>
       <c r="W9">
-        <v>-0.0045</v>
+        <v>-0.0042</v>
       </c>
       <c r="X9">
-        <v>-0.003</v>
+        <v>-0.0036</v>
       </c>
       <c r="Y9">
-        <v>-0.0024</v>
+        <v>-0.0015</v>
       </c>
       <c r="Z9">
         <v>6</v>
       </c>
       <c r="AA9">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="AC9">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="AD9">
         <v>62</v>

--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
@@ -251,10 +251,10 @@
     <t>近距离散射，适合贴脸爆发</t>
   </si>
   <si>
-    <t>Bullet_DemonPurple_Medium_Projectile</t>
-  </si>
-  <si>
-    <t>Bullet_DemonPurple_Medium_Impact</t>
+    <t>Laser_Red_Medium_Projectile</t>
+  </si>
+  <si>
+    <t>Laser_Red_Medium_Impact</t>
   </si>
   <si>
     <t>Gun1</t>
@@ -1457,8 +1457,8 @@
   <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="15" max="15" width="34" customWidth="1"/>
-    <col min="16" max="16" width="25" customWidth="1"/>
+    <col min="15" max="15" width="36.625" customWidth="1"/>
+    <col min="16" max="16" width="34.5" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1856,10 +1856,10 @@
         <v>26</v>
       </c>
       <c r="AE5">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="AF5">
-        <v>1200</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -1951,10 +1951,10 @@
         <v>42</v>
       </c>
       <c r="AE6">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="AF6">
-        <v>1200</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:32">
@@ -1968,13 +1968,13 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7">
         <v>15</v>
       </c>
       <c r="G7">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>20</v>
@@ -2046,10 +2046,10 @@
         <v>56</v>
       </c>
       <c r="AE7">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="AF7">
-        <v>1200</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="8" spans="1:32">
@@ -2141,10 +2141,10 @@
         <v>24</v>
       </c>
       <c r="AE8">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="AF8">
-        <v>1500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="9" spans="1:32">
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H9">
         <v>30</v>
@@ -2236,10 +2236,10 @@
         <v>62</v>
       </c>
       <c r="AE9">
-        <v>1600</v>
+        <v>3000</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" ht="13.5" spans="1:32">

--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
@@ -251,10 +251,10 @@
     <t>近距离散射，适合贴脸爆发</t>
   </si>
   <si>
-    <t>Laser_Red_Medium_Projectile</t>
-  </si>
-  <si>
-    <t>Laser_Red_Medium_Impact</t>
+    <t>Laser_Red_Small_Projectile</t>
+  </si>
+  <si>
+    <t>Laser_Red_Small_Impact</t>
   </si>
   <si>
     <t>Gun1</t>
@@ -1832,25 +1832,25 @@
         <v>77</v>
       </c>
       <c r="W5">
-        <v>-0.0042</v>
+        <v>0.205</v>
       </c>
       <c r="X5">
-        <v>-0.0036</v>
+        <v>0.362</v>
       </c>
       <c r="Y5">
-        <v>-0.0015</v>
+        <v>-0.233</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>-18.065</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>-101.5</v>
       </c>
       <c r="AB5">
-        <v>-90</v>
+        <v>149.519</v>
       </c>
       <c r="AC5">
-        <v>0.38</v>
+        <v>46.4</v>
       </c>
       <c r="AD5">
         <v>26</v>
@@ -1927,25 +1927,25 @@
         <v>77</v>
       </c>
       <c r="W6">
-        <v>-0.0042</v>
+        <v>0.205</v>
       </c>
       <c r="X6">
-        <v>-0.0036</v>
+        <v>0.362</v>
       </c>
       <c r="Y6">
-        <v>-0.0015</v>
+        <v>-0.233</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>-18.065</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>-101.5</v>
       </c>
       <c r="AB6">
-        <v>-90</v>
+        <v>149.519</v>
       </c>
       <c r="AC6">
-        <v>0.38</v>
+        <v>46.4</v>
       </c>
       <c r="AD6">
         <v>42</v>
@@ -2022,25 +2022,25 @@
         <v>77</v>
       </c>
       <c r="W7">
-        <v>-0.0042</v>
+        <v>0.205</v>
       </c>
       <c r="X7">
-        <v>-0.0036</v>
+        <v>0.362</v>
       </c>
       <c r="Y7">
-        <v>-0.0015</v>
+        <v>-0.233</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>-18.065</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>-101.5</v>
       </c>
       <c r="AB7">
-        <v>-90</v>
+        <v>149.519</v>
       </c>
       <c r="AC7">
-        <v>0.38</v>
+        <v>46.4</v>
       </c>
       <c r="AD7">
         <v>56</v>
@@ -2117,25 +2117,25 @@
         <v>77</v>
       </c>
       <c r="W8">
-        <v>-0.0042</v>
+        <v>0.205</v>
       </c>
       <c r="X8">
-        <v>-0.0036</v>
+        <v>0.362</v>
       </c>
       <c r="Y8">
-        <v>-0.0015</v>
+        <v>-0.233</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>-18.065</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>-101.5</v>
       </c>
       <c r="AB8">
-        <v>-90</v>
+        <v>149.519</v>
       </c>
       <c r="AC8">
-        <v>0.38</v>
+        <v>46.4</v>
       </c>
       <c r="AD8">
         <v>24</v>
@@ -2212,25 +2212,25 @@
         <v>77</v>
       </c>
       <c r="W9">
-        <v>-0.0042</v>
+        <v>0.205</v>
       </c>
       <c r="X9">
-        <v>-0.0036</v>
+        <v>0.362</v>
       </c>
       <c r="Y9">
-        <v>-0.0015</v>
+        <v>-0.233</v>
       </c>
       <c r="Z9">
-        <v>6</v>
+        <v>-18.065</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>-101.5</v>
       </c>
       <c r="AB9">
-        <v>-90</v>
+        <v>149.519</v>
       </c>
       <c r="AC9">
-        <v>0.38</v>
+        <v>46.4</v>
       </c>
       <c r="AD9">
         <v>62</v>

--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="106">
   <si>
     <t>##var</t>
   </si>
@@ -125,6 +125,18 @@
     <t>HitEffectDurationMs</t>
   </si>
   <si>
+    <t>FireAnimationType</t>
+  </si>
+  <si>
+    <t>MuzzleFlashEffect</t>
+  </si>
+  <si>
+    <t>MuzzleFlashDurationMs</t>
+  </si>
+  <si>
+    <t>HitFlashDurationMs</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -245,10 +257,22 @@
     <t>命中特效持续时间(毫秒)</t>
   </si>
   <si>
-    <t>霰弹枪1号</t>
-  </si>
-  <si>
-    <t>近距离散射，适合贴脸爆发</t>
+    <t>射击动画类型(1=单发,2=连发)</t>
+  </si>
+  <si>
+    <t>枪口火焰特效Prefab名(空=不显示)</t>
+  </si>
+  <si>
+    <t>枪口火焰持续时间(毫秒)</t>
+  </si>
+  <si>
+    <t>命中闪光时长(毫秒)</t>
+  </si>
+  <si>
+    <t>锋刃 自动步枪</t>
+  </si>
+  <si>
+    <t>中距连发自动步枪，均衡火力</t>
   </si>
   <si>
     <t>Laser_Red_Small_Projectile</t>
@@ -263,28 +287,64 @@
     <t>Muzzle</t>
   </si>
   <si>
-    <t>步枪1号</t>
-  </si>
-  <si>
-    <t>高伤害单发，锁定追踪目标</t>
-  </si>
-  <si>
-    <t>步枪2号</t>
-  </si>
-  <si>
-    <t>高射速连发，适合持续压制</t>
-  </si>
-  <si>
-    <t>火箭炮1号</t>
-  </si>
-  <si>
-    <t>高爆发范围伤害，换弹较慢</t>
-  </si>
-  <si>
-    <t>冲锋枪</t>
-  </si>
-  <si>
-    <t>可移动射击，机动性强</t>
+    <t>瞬息 自动步枪</t>
+  </si>
+  <si>
+    <t>高散射自动步枪，适合中近距</t>
+  </si>
+  <si>
+    <t>气泡 冲锋枪</t>
+  </si>
+  <si>
+    <t>可移动射击冲锋枪，高机动</t>
+  </si>
+  <si>
+    <t>蜂鸣 冲锋枪</t>
+  </si>
+  <si>
+    <t>快速换弹冲锋枪，持续输出</t>
+  </si>
+  <si>
+    <t>砰砰 散弹枪</t>
+  </si>
+  <si>
+    <t>可移动近距散弹枪，爆发伤害</t>
+  </si>
+  <si>
+    <t>碎灭 散弹枪</t>
+  </si>
+  <si>
+    <t>远距重型散弹枪，高单发伤害</t>
+  </si>
+  <si>
+    <t>肃静 狙击步枪</t>
+  </si>
+  <si>
+    <t>远距高伤狙击，适合精确打击</t>
+  </si>
+  <si>
+    <t>咬合 狙击步枪</t>
+  </si>
+  <si>
+    <t>追踪锁定狙击，弹容量大</t>
+  </si>
+  <si>
+    <t>游侠 手枪</t>
+  </si>
+  <si>
+    <t>可移动射击手枪，均衡副武器</t>
+  </si>
+  <si>
+    <t>爆裂 榴弹炮</t>
+  </si>
+  <si>
+    <t>位置锁定榴弹，范围爆发伤害</t>
+  </si>
+  <si>
+    <t>熔点 射线枪</t>
+  </si>
+  <si>
+    <t>持续射线武器，高射速低单发</t>
   </si>
 </sst>
 </file>
@@ -297,11 +357,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -309,11 +371,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -762,7 +819,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -778,149 +835,138 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -973,221 +1019,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1197,7 +1029,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1207,39 +1039,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1318,503 +1150,601 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF12"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="15" max="15" width="36.625" customWidth="1"/>
-    <col min="16" max="16" width="34.5" customWidth="1"/>
-    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="11" max="11" width="38.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="42.75" spans="1:32">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:36">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="R2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="S2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="U2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="V2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="W2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="X2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Y2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Z2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AA2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AB2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AC2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AD2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AE2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AF2" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:36">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="84.75" spans="1:32">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="2" t="s">
+    <row r="4" spans="1:36">
+      <c r="A4" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="B4" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="C4" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="D4" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="E4" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="F4" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="G4" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="H4" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="I4" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="J4" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="K4" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="L4" t="s">
         <v>55</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="M4" t="s">
         <v>56</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="N4" t="s">
         <v>57</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="O4" t="s">
         <v>58</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="P4" t="s">
         <v>59</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="Q4" t="s">
         <v>60</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="R4" t="s">
         <v>61</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="S4" t="s">
         <v>62</v>
       </c>
-      <c r="X4" s="2" t="s">
+      <c r="T4" t="s">
         <v>63</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="U4" t="s">
         <v>64</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="V4" t="s">
         <v>65</v>
       </c>
-      <c r="AA4" s="2" t="s">
+      <c r="W4" t="s">
         <v>66</v>
       </c>
-      <c r="AB4" s="2" t="s">
+      <c r="X4" t="s">
         <v>67</v>
       </c>
-      <c r="AC4" s="2" t="s">
+      <c r="Y4" t="s">
         <v>68</v>
       </c>
-      <c r="AD4" s="2" t="s">
+      <c r="Z4" t="s">
         <v>69</v>
       </c>
-      <c r="AE4" s="2" t="s">
+      <c r="AA4" t="s">
         <v>70</v>
       </c>
-      <c r="AF4" s="2" t="s">
+      <c r="AB4" t="s">
         <v>71</v>
       </c>
+      <c r="AC4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:36">
       <c r="B5">
-        <v>50009</v>
+        <v>50001</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>20</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I5">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="N5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="O5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="Q5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -1829,7 +1759,7 @@
         <v>4</v>
       </c>
       <c r="V5" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="W5">
         <v>0.205</v>
@@ -1853,7 +1783,7 @@
         <v>46.4</v>
       </c>
       <c r="AD5">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AE5">
         <v>3000</v>
@@ -1861,55 +1791,67 @@
       <c r="AF5">
         <v>5000</v>
       </c>
+      <c r="AG5">
+        <v>2</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI5">
+        <v>150</v>
+      </c>
+      <c r="AJ5">
+        <v>150</v>
+      </c>
     </row>
-    <row r="6" spans="1:32">
+    <row r="6" spans="1:36">
       <c r="B6">
-        <v>50010</v>
+        <v>50002</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>1</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="O6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="Q6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -1924,7 +1866,7 @@
         <v>4</v>
       </c>
       <c r="V6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="W6">
         <v>0.205</v>
@@ -1956,55 +1898,67 @@
       <c r="AF6">
         <v>5000</v>
       </c>
+      <c r="AG6">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI6">
+        <v>150</v>
+      </c>
+      <c r="AJ6">
+        <v>150</v>
+      </c>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:36">
       <c r="B7">
-        <v>50011</v>
+        <v>50003</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7">
+        <v>25</v>
+      </c>
+      <c r="I7">
+        <v>1500</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
         <v>20</v>
       </c>
-      <c r="I7">
-        <v>2400</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
       <c r="N7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="O7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="Q7" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2019,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="V7" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="W7">
         <v>0.205</v>
@@ -2051,34 +2005,46 @@
       <c r="AF7">
         <v>5000</v>
       </c>
+      <c r="AG7">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI7">
+        <v>150</v>
+      </c>
+      <c r="AJ7">
+        <v>150</v>
+      </c>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:36">
       <c r="B8">
-        <v>50012</v>
+        <v>50004</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
         <v>100</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>20</v>
       </c>
-      <c r="G8">
-        <v>3000</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
       <c r="I8">
-        <v>3200</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>3</v>
@@ -2087,19 +2053,19 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N8" t="s">
+        <v>91</v>
+      </c>
+      <c r="O8" t="s">
+        <v>82</v>
+      </c>
+      <c r="P8" t="s">
         <v>83</v>
       </c>
-      <c r="O8" t="s">
-        <v>74</v>
-      </c>
-      <c r="P8" t="s">
-        <v>75</v>
-      </c>
       <c r="Q8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2114,7 +2080,7 @@
         <v>4</v>
       </c>
       <c r="V8" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="W8">
         <v>0.205</v>
@@ -2138,7 +2104,7 @@
         <v>46.4</v>
       </c>
       <c r="AD8">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="AE8">
         <v>3000</v>
@@ -2146,55 +2112,67 @@
       <c r="AF8">
         <v>5000</v>
       </c>
+      <c r="AG8">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI8">
+        <v>150</v>
+      </c>
+      <c r="AJ8">
+        <v>150</v>
+      </c>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:36">
       <c r="B9">
-        <v>50013</v>
-      </c>
-      <c r="C9" s="4" t="s">
+        <v>50005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>800</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>2000</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <v>50</v>
+      </c>
+      <c r="N9" t="s">
+        <v>93</v>
+      </c>
+      <c r="O9" t="s">
+        <v>82</v>
+      </c>
+      <c r="P9" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q9" t="s">
         <v>84</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>14</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>50</v>
-      </c>
-      <c r="H9">
-        <v>30</v>
-      </c>
-      <c r="I9">
-        <v>1600</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>20</v>
-      </c>
-      <c r="N9" t="s">
-        <v>85</v>
-      </c>
-      <c r="O9" t="s">
-        <v>74</v>
-      </c>
-      <c r="P9" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>76</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2209,7 +2187,7 @@
         <v>4</v>
       </c>
       <c r="V9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="W9">
         <v>0.205</v>
@@ -2233,7 +2211,7 @@
         <v>46.4</v>
       </c>
       <c r="AD9">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="AE9">
         <v>3000</v>
@@ -2241,21 +2219,666 @@
       <c r="AF9">
         <v>5000</v>
       </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI9">
+        <v>150</v>
+      </c>
+      <c r="AJ9">
+        <v>150</v>
+      </c>
     </row>
-    <row r="11" s="3" customFormat="1" ht="13.5" spans="1:32">
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+    <row r="10" spans="1:36">
+      <c r="B10">
+        <v>50006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>6</v>
+      </c>
+      <c r="G10">
+        <v>1500</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>2500</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>5</v>
+      </c>
+      <c r="M10">
+        <v>25</v>
+      </c>
+      <c r="N10" t="s">
+        <v>95</v>
+      </c>
+      <c r="O10" t="s">
+        <v>82</v>
+      </c>
+      <c r="P10" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>84</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>9</v>
+      </c>
+      <c r="T10">
+        <v>6</v>
+      </c>
+      <c r="U10">
+        <v>4</v>
+      </c>
+      <c r="V10" t="s">
+        <v>85</v>
+      </c>
+      <c r="W10">
+        <v>0.205</v>
+      </c>
+      <c r="X10">
+        <v>0.362</v>
+      </c>
+      <c r="Y10">
+        <v>-0.233</v>
+      </c>
+      <c r="Z10">
+        <v>-18.065</v>
+      </c>
+      <c r="AA10">
+        <v>-101.5</v>
+      </c>
+      <c r="AB10">
+        <v>149.519</v>
+      </c>
+      <c r="AC10">
+        <v>46.4</v>
+      </c>
+      <c r="AD10">
+        <v>26</v>
+      </c>
+      <c r="AE10">
+        <v>3000</v>
+      </c>
+      <c r="AF10">
+        <v>5000</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI10">
+        <v>150</v>
+      </c>
+      <c r="AJ10">
+        <v>150</v>
+      </c>
     </row>
-    <row r="12" s="3" customFormat="1" ht="13.5"/>
+    <row r="11" spans="1:36">
+      <c r="B11">
+        <v>50007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
+        <v>300</v>
+      </c>
+      <c r="F11">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>1500</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>4000</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
+      <c r="N11" t="s">
+        <v>97</v>
+      </c>
+      <c r="O11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P11" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>84</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>9</v>
+      </c>
+      <c r="T11">
+        <v>6</v>
+      </c>
+      <c r="U11">
+        <v>4</v>
+      </c>
+      <c r="V11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W11">
+        <v>0.205</v>
+      </c>
+      <c r="X11">
+        <v>0.362</v>
+      </c>
+      <c r="Y11">
+        <v>-0.233</v>
+      </c>
+      <c r="Z11">
+        <v>-18.065</v>
+      </c>
+      <c r="AA11">
+        <v>-101.5</v>
+      </c>
+      <c r="AB11">
+        <v>149.519</v>
+      </c>
+      <c r="AC11">
+        <v>46.4</v>
+      </c>
+      <c r="AD11">
+        <v>62</v>
+      </c>
+      <c r="AE11">
+        <v>3000</v>
+      </c>
+      <c r="AF11">
+        <v>5000</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI11">
+        <v>150</v>
+      </c>
+      <c r="AJ11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36">
+      <c r="B12">
+        <v>50008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>300</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>2000</v>
+      </c>
+      <c r="H12">
+        <v>8</v>
+      </c>
+      <c r="I12">
+        <v>4000</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>5</v>
+      </c>
+      <c r="N12" t="s">
+        <v>99</v>
+      </c>
+      <c r="O12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P12" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>84</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>9</v>
+      </c>
+      <c r="T12">
+        <v>6</v>
+      </c>
+      <c r="U12">
+        <v>4</v>
+      </c>
+      <c r="V12" t="s">
+        <v>85</v>
+      </c>
+      <c r="W12">
+        <v>0.205</v>
+      </c>
+      <c r="X12">
+        <v>0.362</v>
+      </c>
+      <c r="Y12">
+        <v>-0.233</v>
+      </c>
+      <c r="Z12">
+        <v>-18.065</v>
+      </c>
+      <c r="AA12">
+        <v>-101.5</v>
+      </c>
+      <c r="AB12">
+        <v>149.519</v>
+      </c>
+      <c r="AC12">
+        <v>46.4</v>
+      </c>
+      <c r="AD12">
+        <v>62</v>
+      </c>
+      <c r="AE12">
+        <v>3000</v>
+      </c>
+      <c r="AF12">
+        <v>5000</v>
+      </c>
+      <c r="AG12">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI12">
+        <v>150</v>
+      </c>
+      <c r="AJ12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36">
+      <c r="B13">
+        <v>50009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>500</v>
+      </c>
+      <c r="H13">
+        <v>8</v>
+      </c>
+      <c r="I13">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>101</v>
+      </c>
+      <c r="O13" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>84</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>9</v>
+      </c>
+      <c r="T13">
+        <v>6</v>
+      </c>
+      <c r="U13">
+        <v>4</v>
+      </c>
+      <c r="V13" t="s">
+        <v>85</v>
+      </c>
+      <c r="W13">
+        <v>0.205</v>
+      </c>
+      <c r="X13">
+        <v>0.362</v>
+      </c>
+      <c r="Y13">
+        <v>-0.233</v>
+      </c>
+      <c r="Z13">
+        <v>-18.065</v>
+      </c>
+      <c r="AA13">
+        <v>-101.5</v>
+      </c>
+      <c r="AB13">
+        <v>149.519</v>
+      </c>
+      <c r="AC13">
+        <v>46.4</v>
+      </c>
+      <c r="AD13">
+        <v>42</v>
+      </c>
+      <c r="AE13">
+        <v>3000</v>
+      </c>
+      <c r="AF13">
+        <v>5000</v>
+      </c>
+      <c r="AG13">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI13">
+        <v>150</v>
+      </c>
+      <c r="AJ13">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36">
+      <c r="B14">
+        <v>50010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>40</v>
+      </c>
+      <c r="F14">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>400</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+      <c r="I14">
+        <v>4000</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>3</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>15</v>
+      </c>
+      <c r="N14" t="s">
+        <v>103</v>
+      </c>
+      <c r="O14" t="s">
+        <v>82</v>
+      </c>
+      <c r="P14" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>84</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>9</v>
+      </c>
+      <c r="T14">
+        <v>6</v>
+      </c>
+      <c r="U14">
+        <v>4</v>
+      </c>
+      <c r="V14" t="s">
+        <v>85</v>
+      </c>
+      <c r="W14">
+        <v>0.205</v>
+      </c>
+      <c r="X14">
+        <v>0.362</v>
+      </c>
+      <c r="Y14">
+        <v>-0.233</v>
+      </c>
+      <c r="Z14">
+        <v>-18.065</v>
+      </c>
+      <c r="AA14">
+        <v>-101.5</v>
+      </c>
+      <c r="AB14">
+        <v>149.519</v>
+      </c>
+      <c r="AC14">
+        <v>46.4</v>
+      </c>
+      <c r="AD14">
+        <v>24</v>
+      </c>
+      <c r="AE14">
+        <v>3000</v>
+      </c>
+      <c r="AF14">
+        <v>5000</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI14">
+        <v>150</v>
+      </c>
+      <c r="AJ14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36">
+      <c r="B15">
+        <v>50011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <v>15</v>
+      </c>
+      <c r="I15">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>105</v>
+      </c>
+      <c r="O15" t="s">
+        <v>82</v>
+      </c>
+      <c r="P15" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>9</v>
+      </c>
+      <c r="T15">
+        <v>6</v>
+      </c>
+      <c r="U15">
+        <v>4</v>
+      </c>
+      <c r="V15" t="s">
+        <v>85</v>
+      </c>
+      <c r="W15">
+        <v>0.205</v>
+      </c>
+      <c r="X15">
+        <v>0.362</v>
+      </c>
+      <c r="Y15">
+        <v>-0.233</v>
+      </c>
+      <c r="Z15">
+        <v>-18.065</v>
+      </c>
+      <c r="AA15">
+        <v>-101.5</v>
+      </c>
+      <c r="AB15">
+        <v>149.519</v>
+      </c>
+      <c r="AC15">
+        <v>46.4</v>
+      </c>
+      <c r="AD15">
+        <v>80</v>
+      </c>
+      <c r="AE15">
+        <v>3000</v>
+      </c>
+      <c r="AF15">
+        <v>5000</v>
+      </c>
+      <c r="AG15">
+        <v>2</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI15">
+        <v>150</v>
+      </c>
+      <c r="AJ15">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:AJ3 A4:J4 L4:AJ4 A5:AJ15" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/Weapon.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t>##var</t>
   </si>
@@ -275,30 +275,39 @@
     <t>中距连发自动步枪，均衡火力</t>
   </si>
   <si>
+    <t>Minigun Bullet</t>
+  </si>
+  <si>
+    <t>Minigun Hit Particle</t>
+  </si>
+  <si>
+    <t>Gun1</t>
+  </si>
+  <si>
+    <t>Muzzle</t>
+  </si>
+  <si>
+    <t>Minigun_muzzle</t>
+  </si>
+  <si>
+    <t>瞬息 自动步枪</t>
+  </si>
+  <si>
+    <t>高散射自动步枪，适合中近距</t>
+  </si>
+  <si>
+    <t>气泡 冲锋枪</t>
+  </si>
+  <si>
+    <t>可移动射击冲锋枪，高机动</t>
+  </si>
+  <si>
     <t>Laser_Red_Small_Projectile</t>
   </si>
   <si>
     <t>Laser_Red_Small_Impact</t>
   </si>
   <si>
-    <t>Gun1</t>
-  </si>
-  <si>
-    <t>Muzzle</t>
-  </si>
-  <si>
-    <t>瞬息 自动步枪</t>
-  </si>
-  <si>
-    <t>高散射自动步枪，适合中近距</t>
-  </si>
-  <si>
-    <t>气泡 冲锋枪</t>
-  </si>
-  <si>
-    <t>可移动射击冲锋枪，高机动</t>
-  </si>
-  <si>
     <t>蜂鸣 冲锋枪</t>
   </si>
   <si>
@@ -311,6 +320,15 @@
     <t>可移动近距散弹枪，爆发伤害</t>
   </si>
   <si>
+    <t>Shotgun Bullet</t>
+  </si>
+  <si>
+    <t>Shotgun Hit Particle</t>
+  </si>
+  <si>
+    <t>Shotgun_muzzle</t>
+  </si>
+  <si>
     <t>碎灭 散弹枪</t>
   </si>
   <si>
@@ -341,10 +359,28 @@
     <t>位置锁定榴弹，范围爆发伤害</t>
   </si>
   <si>
+    <t>Lava Bullet</t>
+  </si>
+  <si>
+    <t>Lava Hit</t>
+  </si>
+  <si>
+    <t>Lava Muzzle</t>
+  </si>
+  <si>
     <t>熔点 射线枪</t>
   </si>
   <si>
     <t>持续射线武器，高射速低单发</t>
+  </si>
+  <si>
+    <t>Tesla Bullet</t>
+  </si>
+  <si>
+    <t>Tesla Hit Particle</t>
+  </si>
+  <si>
+    <t>Tesla_shot</t>
   </si>
 </sst>
 </file>
@@ -820,153 +856,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1348,7 +1384,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
   <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -1356,1521 +1392,1521 @@
     <col min="11" max="11" width="38.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="0" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:36">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AG2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AH2" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AI2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" s="0" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:36">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="0" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:36">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U4" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="Z4" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AA4" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AD4" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AE4" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AF4" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AG4" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AH4" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AI4" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AJ4" s="0" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:36">
-      <c r="B5">
+    <row r="5">
+      <c r="B5" s="0">
         <v>50001</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <v>20</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <v>8</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="0">
         <v>200</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="0">
         <v>25</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="0">
         <v>2000</v>
       </c>
-      <c r="J5" t="b">
+      <c r="J5" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="0">
         <v>2</v>
       </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="0">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0">
         <v>5</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
+      <c r="R5" s="0">
+        <v>1</v>
+      </c>
+      <c r="S5" s="0">
         <v>9</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="0">
         <v>6</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="0">
         <v>4</v>
       </c>
-      <c r="V5" t="s">
+      <c r="V5" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="0">
         <v>0.205</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="0">
         <v>0.362</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="0">
         <v>-0.233</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="0">
         <v>-18.065</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="0">
         <v>-101.5</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="0">
         <v>149.519</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="0">
         <v>46.4</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="0">
         <v>42</v>
       </c>
-      <c r="AE5">
+      <c r="AE5" s="0">
         <v>3000</v>
       </c>
-      <c r="AF5">
+      <c r="AF5" s="0">
+        <v>1200</v>
+      </c>
+      <c r="AG5" s="0">
+        <v>2</v>
+      </c>
+      <c r="AH5" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI5" s="0">
+        <v>150</v>
+      </c>
+      <c r="AJ5" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0">
+        <v>50002</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="0">
+        <v>6</v>
+      </c>
+      <c r="E6" s="0">
+        <v>20</v>
+      </c>
+      <c r="F6" s="0">
+        <v>6</v>
+      </c>
+      <c r="G6" s="0">
+        <v>150</v>
+      </c>
+      <c r="H6" s="0">
+        <v>20</v>
+      </c>
+      <c r="I6" s="0">
+        <v>3000</v>
+      </c>
+      <c r="J6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0">
+        <v>2</v>
+      </c>
+      <c r="L6" s="0">
+        <v>1</v>
+      </c>
+      <c r="M6" s="0">
+        <v>15</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q6" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" s="0">
+        <v>1</v>
+      </c>
+      <c r="S6" s="0">
+        <v>9</v>
+      </c>
+      <c r="T6" s="0">
+        <v>6</v>
+      </c>
+      <c r="U6" s="0">
+        <v>4</v>
+      </c>
+      <c r="V6" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="W6" s="0">
+        <v>0.205</v>
+      </c>
+      <c r="X6" s="0">
+        <v>0.362</v>
+      </c>
+      <c r="Y6" s="0">
+        <v>-0.233</v>
+      </c>
+      <c r="Z6" s="0">
+        <v>-18.065</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>-101.5</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>149.519</v>
+      </c>
+      <c r="AC6" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="AD6" s="0">
+        <v>42</v>
+      </c>
+      <c r="AE6" s="0">
+        <v>3000</v>
+      </c>
+      <c r="AF6" s="0">
+        <v>1200</v>
+      </c>
+      <c r="AG6" s="0">
+        <v>2</v>
+      </c>
+      <c r="AH6" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI6" s="0">
+        <v>150</v>
+      </c>
+      <c r="AJ6" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0">
+        <v>50003</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="0">
+        <v>5</v>
+      </c>
+      <c r="E7" s="0">
+        <v>15</v>
+      </c>
+      <c r="F7" s="0">
+        <v>6</v>
+      </c>
+      <c r="G7" s="0">
+        <v>100</v>
+      </c>
+      <c r="H7" s="0">
+        <v>25</v>
+      </c>
+      <c r="I7" s="0">
+        <v>1500</v>
+      </c>
+      <c r="J7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="0">
+        <v>3</v>
+      </c>
+      <c r="L7" s="0">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0">
+        <v>20</v>
+      </c>
+      <c r="N7" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="O7" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="P7" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q7" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="0">
+        <v>1</v>
+      </c>
+      <c r="S7" s="0">
+        <v>9</v>
+      </c>
+      <c r="T7" s="0">
+        <v>6</v>
+      </c>
+      <c r="U7" s="0">
+        <v>4</v>
+      </c>
+      <c r="V7" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="W7" s="0">
+        <v>0.205</v>
+      </c>
+      <c r="X7" s="0">
+        <v>0.362</v>
+      </c>
+      <c r="Y7" s="0">
+        <v>-0.233</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>-18.065</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>-101.5</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>149.519</v>
+      </c>
+      <c r="AC7" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="AD7" s="0">
+        <v>56</v>
+      </c>
+      <c r="AE7" s="0">
+        <v>3000</v>
+      </c>
+      <c r="AF7" s="0">
         <v>5000</v>
       </c>
-      <c r="AG5">
+      <c r="AG7" s="0">
         <v>2</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AH7" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="AI5">
+      <c r="AI7" s="0">
         <v>150</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ7" s="0">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
-      <c r="B6">
-        <v>50002</v>
-      </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6">
+    <row r="8">
+      <c r="B8" s="0">
+        <v>50004</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="0">
+        <v>5</v>
+      </c>
+      <c r="E8" s="0">
+        <v>15</v>
+      </c>
+      <c r="F8" s="0">
         <v>6</v>
       </c>
-      <c r="E6">
+      <c r="G8" s="0">
+        <v>100</v>
+      </c>
+      <c r="H8" s="0">
         <v>20</v>
       </c>
-      <c r="F6">
+      <c r="I8" s="0">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="0">
+        <v>3</v>
+      </c>
+      <c r="L8" s="0">
+        <v>1</v>
+      </c>
+      <c r="M8" s="0">
+        <v>20</v>
+      </c>
+      <c r="N8" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="O8" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="P8" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" s="0">
+        <v>1</v>
+      </c>
+      <c r="S8" s="0">
+        <v>9</v>
+      </c>
+      <c r="T8" s="0">
         <v>6</v>
       </c>
-      <c r="G6">
+      <c r="U8" s="0">
+        <v>4</v>
+      </c>
+      <c r="V8" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="W8" s="0">
+        <v>0.205</v>
+      </c>
+      <c r="X8" s="0">
+        <v>0.362</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>-0.233</v>
+      </c>
+      <c r="Z8" s="0">
+        <v>-18.065</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>-101.5</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>149.519</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="AD8" s="0">
+        <v>56</v>
+      </c>
+      <c r="AE8" s="0">
+        <v>3000</v>
+      </c>
+      <c r="AF8" s="0">
+        <v>5000</v>
+      </c>
+      <c r="AG8" s="0">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI8" s="0">
         <v>150</v>
       </c>
-      <c r="H6">
-        <v>20</v>
-      </c>
-      <c r="I6">
+      <c r="AJ8" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0">
+        <v>50005</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="0">
+        <v>1</v>
+      </c>
+      <c r="E9" s="0">
+        <v>40</v>
+      </c>
+      <c r="F9" s="0">
+        <v>4</v>
+      </c>
+      <c r="G9" s="0">
+        <v>800</v>
+      </c>
+      <c r="H9" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" s="0">
+        <v>2000</v>
+      </c>
+      <c r="J9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="0">
+        <v>2</v>
+      </c>
+      <c r="L9" s="0">
+        <v>5</v>
+      </c>
+      <c r="M9" s="0">
+        <v>50</v>
+      </c>
+      <c r="N9" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="O9" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="P9" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="R9" s="0">
+        <v>1</v>
+      </c>
+      <c r="S9" s="0">
+        <v>9</v>
+      </c>
+      <c r="T9" s="0">
+        <v>6</v>
+      </c>
+      <c r="U9" s="0">
+        <v>4</v>
+      </c>
+      <c r="V9" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="W9" s="0">
+        <v>0.205</v>
+      </c>
+      <c r="X9" s="0">
+        <v>0.362</v>
+      </c>
+      <c r="Y9" s="0">
+        <v>-0.233</v>
+      </c>
+      <c r="Z9" s="0">
+        <v>-18.065</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>-101.5</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>149.519</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="AD9" s="0">
+        <v>26</v>
+      </c>
+      <c r="AE9" s="0">
         <v>3000</v>
       </c>
-      <c r="J6" t="b">
+      <c r="AF9" s="0">
+        <v>1200</v>
+      </c>
+      <c r="AG9" s="0">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI9" s="0">
+        <v>150</v>
+      </c>
+      <c r="AJ9" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0">
+        <v>50006</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="0">
+        <v>1</v>
+      </c>
+      <c r="E10" s="0">
+        <v>50</v>
+      </c>
+      <c r="F10" s="0">
+        <v>6</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1500</v>
+      </c>
+      <c r="H10" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" s="0">
+        <v>2500</v>
+      </c>
+      <c r="J10" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K10" s="0">
         <v>2</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+      <c r="L10" s="0">
+        <v>5</v>
+      </c>
+      <c r="M10" s="0">
+        <v>25</v>
+      </c>
+      <c r="N10" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="P10" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q10" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="R10" s="0">
+        <v>1</v>
+      </c>
+      <c r="S10" s="0">
+        <v>9</v>
+      </c>
+      <c r="T10" s="0">
+        <v>6</v>
+      </c>
+      <c r="U10" s="0">
+        <v>4</v>
+      </c>
+      <c r="V10" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="W10" s="0">
+        <v>0.205</v>
+      </c>
+      <c r="X10" s="0">
+        <v>0.362</v>
+      </c>
+      <c r="Y10" s="0">
+        <v>-0.233</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>-18.065</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>-101.5</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>149.519</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="AD10" s="0">
+        <v>26</v>
+      </c>
+      <c r="AE10" s="0">
+        <v>3000</v>
+      </c>
+      <c r="AF10" s="0">
+        <v>1200</v>
+      </c>
+      <c r="AG10" s="0">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI10" s="0">
+        <v>150</v>
+      </c>
+      <c r="AJ10" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0">
+        <v>50007</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="0">
+        <v>7</v>
+      </c>
+      <c r="E11" s="0">
+        <v>300</v>
+      </c>
+      <c r="F11" s="0">
+        <v>12</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1500</v>
+      </c>
+      <c r="H11" s="0">
+        <v>5</v>
+      </c>
+      <c r="I11" s="0">
+        <v>4000</v>
+      </c>
+      <c r="J11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0">
+        <v>2</v>
+      </c>
+      <c r="L11" s="0">
+        <v>1</v>
+      </c>
+      <c r="M11" s="0">
+        <v>5</v>
+      </c>
+      <c r="N11" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q11" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="R11" s="0">
+        <v>1</v>
+      </c>
+      <c r="S11" s="0">
+        <v>9</v>
+      </c>
+      <c r="T11" s="0">
+        <v>6</v>
+      </c>
+      <c r="U11" s="0">
+        <v>4</v>
+      </c>
+      <c r="V11" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="W11" s="0">
+        <v>0.205</v>
+      </c>
+      <c r="X11" s="0">
+        <v>0.362</v>
+      </c>
+      <c r="Y11" s="0">
+        <v>-0.233</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>-18.065</v>
+      </c>
+      <c r="AA11" s="0">
+        <v>-101.5</v>
+      </c>
+      <c r="AB11" s="0">
+        <v>149.519</v>
+      </c>
+      <c r="AC11" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="AD11" s="0">
+        <v>62</v>
+      </c>
+      <c r="AE11" s="0">
+        <v>3000</v>
+      </c>
+      <c r="AF11" s="0">
+        <v>5000</v>
+      </c>
+      <c r="AG11" s="0">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI11" s="0">
+        <v>150</v>
+      </c>
+      <c r="AJ11" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0">
+        <v>50008</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="0">
+        <v>7</v>
+      </c>
+      <c r="E12" s="0">
+        <v>300</v>
+      </c>
+      <c r="F12" s="0">
+        <v>8</v>
+      </c>
+      <c r="G12" s="0">
+        <v>2000</v>
+      </c>
+      <c r="H12" s="0">
+        <v>8</v>
+      </c>
+      <c r="I12" s="0">
+        <v>4000</v>
+      </c>
+      <c r="J12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0">
+        <v>1</v>
+      </c>
+      <c r="L12" s="0">
+        <v>1</v>
+      </c>
+      <c r="M12" s="0">
+        <v>5</v>
+      </c>
+      <c r="N12" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q12" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="R12" s="0">
+        <v>1</v>
+      </c>
+      <c r="S12" s="0">
+        <v>9</v>
+      </c>
+      <c r="T12" s="0">
+        <v>6</v>
+      </c>
+      <c r="U12" s="0">
+        <v>4</v>
+      </c>
+      <c r="V12" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="W12" s="0">
+        <v>0.205</v>
+      </c>
+      <c r="X12" s="0">
+        <v>0.362</v>
+      </c>
+      <c r="Y12" s="0">
+        <v>-0.233</v>
+      </c>
+      <c r="Z12" s="0">
+        <v>-18.065</v>
+      </c>
+      <c r="AA12" s="0">
+        <v>-101.5</v>
+      </c>
+      <c r="AB12" s="0">
+        <v>149.519</v>
+      </c>
+      <c r="AC12" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="AD12" s="0">
+        <v>62</v>
+      </c>
+      <c r="AE12" s="0">
+        <v>3000</v>
+      </c>
+      <c r="AF12" s="0">
+        <v>5000</v>
+      </c>
+      <c r="AG12" s="0">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI12" s="0">
+        <v>150</v>
+      </c>
+      <c r="AJ12" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0">
+        <v>50009</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="0">
+        <v>8</v>
+      </c>
+      <c r="E13" s="0">
+        <v>30</v>
+      </c>
+      <c r="F13" s="0">
+        <v>7</v>
+      </c>
+      <c r="G13" s="0">
+        <v>500</v>
+      </c>
+      <c r="H13" s="0">
+        <v>8</v>
+      </c>
+      <c r="I13" s="0">
+        <v>1000</v>
+      </c>
+      <c r="J13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="0">
+        <v>2</v>
+      </c>
+      <c r="L13" s="0">
+        <v>1</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="O13" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="P13" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q13" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="R13" s="0">
+        <v>1</v>
+      </c>
+      <c r="S13" s="0">
+        <v>9</v>
+      </c>
+      <c r="T13" s="0">
+        <v>6</v>
+      </c>
+      <c r="U13" s="0">
+        <v>4</v>
+      </c>
+      <c r="V13" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="W13" s="0">
+        <v>0.205</v>
+      </c>
+      <c r="X13" s="0">
+        <v>0.362</v>
+      </c>
+      <c r="Y13" s="0">
+        <v>-0.233</v>
+      </c>
+      <c r="Z13" s="0">
+        <v>-18.065</v>
+      </c>
+      <c r="AA13" s="0">
+        <v>-101.5</v>
+      </c>
+      <c r="AB13" s="0">
+        <v>149.519</v>
+      </c>
+      <c r="AC13" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="AD13" s="0">
+        <v>42</v>
+      </c>
+      <c r="AE13" s="0">
+        <v>3000</v>
+      </c>
+      <c r="AF13" s="0">
+        <v>5000</v>
+      </c>
+      <c r="AG13" s="0">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI13" s="0">
+        <v>150</v>
+      </c>
+      <c r="AJ13" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0">
+        <v>50010</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="0">
+        <v>9</v>
+      </c>
+      <c r="E14" s="0">
+        <v>40</v>
+      </c>
+      <c r="F14" s="0">
+        <v>9</v>
+      </c>
+      <c r="G14" s="0">
+        <v>400</v>
+      </c>
+      <c r="H14" s="0">
+        <v>6</v>
+      </c>
+      <c r="I14" s="0">
+        <v>4000</v>
+      </c>
+      <c r="J14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0">
+        <v>3</v>
+      </c>
+      <c r="L14" s="0">
+        <v>1</v>
+      </c>
+      <c r="M14" s="0">
         <v>15</v>
       </c>
-      <c r="N6" t="s">
-        <v>87</v>
-      </c>
-      <c r="O6" t="s">
-        <v>82</v>
-      </c>
-      <c r="P6" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q6" t="s">
+      <c r="N14" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="O14" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q14" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
+      <c r="R14" s="0">
+        <v>1</v>
+      </c>
+      <c r="S14" s="0">
         <v>9</v>
       </c>
-      <c r="T6">
+      <c r="T14" s="0">
         <v>6</v>
       </c>
-      <c r="U6">
+      <c r="U14" s="0">
         <v>4</v>
       </c>
-      <c r="V6" t="s">
+      <c r="V14" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="W6">
+      <c r="W14" s="0">
         <v>0.205</v>
       </c>
-      <c r="X6">
+      <c r="X14" s="0">
         <v>0.362</v>
       </c>
-      <c r="Y6">
+      <c r="Y14" s="0">
         <v>-0.233</v>
       </c>
-      <c r="Z6">
+      <c r="Z14" s="0">
         <v>-18.065</v>
       </c>
-      <c r="AA6">
+      <c r="AA14" s="0">
         <v>-101.5</v>
       </c>
-      <c r="AB6">
+      <c r="AB14" s="0">
         <v>149.519</v>
       </c>
-      <c r="AC6">
+      <c r="AC14" s="0">
         <v>46.4</v>
       </c>
-      <c r="AD6">
-        <v>42</v>
-      </c>
-      <c r="AE6">
+      <c r="AD14" s="0">
+        <v>24</v>
+      </c>
+      <c r="AE14" s="0">
         <v>3000</v>
       </c>
-      <c r="AF6">
-        <v>5000</v>
-      </c>
-      <c r="AG6">
+      <c r="AF14" s="0">
+        <v>1200</v>
+      </c>
+      <c r="AG14" s="0">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI14" s="0">
+        <v>150</v>
+      </c>
+      <c r="AJ14" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0">
+        <v>50011</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="0">
+        <v>10</v>
+      </c>
+      <c r="E15" s="0">
+        <v>10</v>
+      </c>
+      <c r="F15" s="0">
+        <v>6</v>
+      </c>
+      <c r="G15" s="0">
+        <v>100</v>
+      </c>
+      <c r="H15" s="0">
+        <v>15</v>
+      </c>
+      <c r="I15" s="0">
+        <v>1000</v>
+      </c>
+      <c r="J15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0">
         <v>2</v>
       </c>
-      <c r="AH6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI6">
+      <c r="L15" s="0">
+        <v>1</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0</v>
+      </c>
+      <c r="N15" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="O15" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q15" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="R15" s="0">
+        <v>1</v>
+      </c>
+      <c r="S15" s="0">
+        <v>9</v>
+      </c>
+      <c r="T15" s="0">
+        <v>6</v>
+      </c>
+      <c r="U15" s="0">
+        <v>4</v>
+      </c>
+      <c r="V15" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="W15" s="0">
+        <v>0.205</v>
+      </c>
+      <c r="X15" s="0">
+        <v>0.362</v>
+      </c>
+      <c r="Y15" s="0">
+        <v>-0.233</v>
+      </c>
+      <c r="Z15" s="0">
+        <v>-18.065</v>
+      </c>
+      <c r="AA15" s="0">
+        <v>-101.5</v>
+      </c>
+      <c r="AB15" s="0">
+        <v>149.519</v>
+      </c>
+      <c r="AC15" s="0">
+        <v>46.4</v>
+      </c>
+      <c r="AD15" s="0">
+        <v>80</v>
+      </c>
+      <c r="AE15" s="0">
+        <v>3000</v>
+      </c>
+      <c r="AF15" s="0">
+        <v>1200</v>
+      </c>
+      <c r="AG15" s="0">
+        <v>2</v>
+      </c>
+      <c r="AH15" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI15" s="0">
         <v>150</v>
       </c>
-      <c r="AJ6">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36">
-      <c r="B7">
-        <v>50003</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>100</v>
-      </c>
-      <c r="H7">
-        <v>25</v>
-      </c>
-      <c r="I7">
-        <v>1500</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>20</v>
-      </c>
-      <c r="N7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O7" t="s">
-        <v>82</v>
-      </c>
-      <c r="P7" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>84</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
-        <v>9</v>
-      </c>
-      <c r="T7">
-        <v>6</v>
-      </c>
-      <c r="U7">
-        <v>4</v>
-      </c>
-      <c r="V7" t="s">
-        <v>85</v>
-      </c>
-      <c r="W7">
-        <v>0.205</v>
-      </c>
-      <c r="X7">
-        <v>0.362</v>
-      </c>
-      <c r="Y7">
-        <v>-0.233</v>
-      </c>
-      <c r="Z7">
-        <v>-18.065</v>
-      </c>
-      <c r="AA7">
-        <v>-101.5</v>
-      </c>
-      <c r="AB7">
-        <v>149.519</v>
-      </c>
-      <c r="AC7">
-        <v>46.4</v>
-      </c>
-      <c r="AD7">
-        <v>56</v>
-      </c>
-      <c r="AE7">
-        <v>3000</v>
-      </c>
-      <c r="AF7">
-        <v>5000</v>
-      </c>
-      <c r="AG7">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI7">
-        <v>150</v>
-      </c>
-      <c r="AJ7">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36">
-      <c r="B8">
-        <v>50004</v>
-      </c>
-      <c r="C8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>6</v>
-      </c>
-      <c r="G8">
-        <v>100</v>
-      </c>
-      <c r="H8">
-        <v>20</v>
-      </c>
-      <c r="I8">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>3</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8" t="s">
-        <v>91</v>
-      </c>
-      <c r="O8" t="s">
-        <v>82</v>
-      </c>
-      <c r="P8" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>84</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>9</v>
-      </c>
-      <c r="T8">
-        <v>6</v>
-      </c>
-      <c r="U8">
-        <v>4</v>
-      </c>
-      <c r="V8" t="s">
-        <v>85</v>
-      </c>
-      <c r="W8">
-        <v>0.205</v>
-      </c>
-      <c r="X8">
-        <v>0.362</v>
-      </c>
-      <c r="Y8">
-        <v>-0.233</v>
-      </c>
-      <c r="Z8">
-        <v>-18.065</v>
-      </c>
-      <c r="AA8">
-        <v>-101.5</v>
-      </c>
-      <c r="AB8">
-        <v>149.519</v>
-      </c>
-      <c r="AC8">
-        <v>46.4</v>
-      </c>
-      <c r="AD8">
-        <v>56</v>
-      </c>
-      <c r="AE8">
-        <v>3000</v>
-      </c>
-      <c r="AF8">
-        <v>5000</v>
-      </c>
-      <c r="AG8">
-        <v>2</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI8">
-        <v>150</v>
-      </c>
-      <c r="AJ8">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36">
-      <c r="B9">
-        <v>50005</v>
-      </c>
-      <c r="C9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>40</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9">
-        <v>800</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>2000</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
-        <v>5</v>
-      </c>
-      <c r="M9">
-        <v>50</v>
-      </c>
-      <c r="N9" t="s">
-        <v>93</v>
-      </c>
-      <c r="O9" t="s">
-        <v>82</v>
-      </c>
-      <c r="P9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>84</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <v>9</v>
-      </c>
-      <c r="T9">
-        <v>6</v>
-      </c>
-      <c r="U9">
-        <v>4</v>
-      </c>
-      <c r="V9" t="s">
-        <v>85</v>
-      </c>
-      <c r="W9">
-        <v>0.205</v>
-      </c>
-      <c r="X9">
-        <v>0.362</v>
-      </c>
-      <c r="Y9">
-        <v>-0.233</v>
-      </c>
-      <c r="Z9">
-        <v>-18.065</v>
-      </c>
-      <c r="AA9">
-        <v>-101.5</v>
-      </c>
-      <c r="AB9">
-        <v>149.519</v>
-      </c>
-      <c r="AC9">
-        <v>46.4</v>
-      </c>
-      <c r="AD9">
-        <v>26</v>
-      </c>
-      <c r="AE9">
-        <v>3000</v>
-      </c>
-      <c r="AF9">
-        <v>5000</v>
-      </c>
-      <c r="AG9">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI9">
-        <v>150</v>
-      </c>
-      <c r="AJ9">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36">
-      <c r="B10">
-        <v>50006</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>50</v>
-      </c>
-      <c r="F10">
-        <v>6</v>
-      </c>
-      <c r="G10">
-        <v>1500</v>
-      </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>2500</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>2</v>
-      </c>
-      <c r="L10">
-        <v>5</v>
-      </c>
-      <c r="M10">
-        <v>25</v>
-      </c>
-      <c r="N10" t="s">
-        <v>95</v>
-      </c>
-      <c r="O10" t="s">
-        <v>82</v>
-      </c>
-      <c r="P10" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>84</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10">
-        <v>9</v>
-      </c>
-      <c r="T10">
-        <v>6</v>
-      </c>
-      <c r="U10">
-        <v>4</v>
-      </c>
-      <c r="V10" t="s">
-        <v>85</v>
-      </c>
-      <c r="W10">
-        <v>0.205</v>
-      </c>
-      <c r="X10">
-        <v>0.362</v>
-      </c>
-      <c r="Y10">
-        <v>-0.233</v>
-      </c>
-      <c r="Z10">
-        <v>-18.065</v>
-      </c>
-      <c r="AA10">
-        <v>-101.5</v>
-      </c>
-      <c r="AB10">
-        <v>149.519</v>
-      </c>
-      <c r="AC10">
-        <v>46.4</v>
-      </c>
-      <c r="AD10">
-        <v>26</v>
-      </c>
-      <c r="AE10">
-        <v>3000</v>
-      </c>
-      <c r="AF10">
-        <v>5000</v>
-      </c>
-      <c r="AG10">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI10">
-        <v>150</v>
-      </c>
-      <c r="AJ10">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36">
-      <c r="B11">
-        <v>50007</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11">
-        <v>7</v>
-      </c>
-      <c r="E11">
-        <v>300</v>
-      </c>
-      <c r="F11">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>1500</v>
-      </c>
-      <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <v>4000</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>5</v>
-      </c>
-      <c r="N11" t="s">
-        <v>97</v>
-      </c>
-      <c r="O11" t="s">
-        <v>82</v>
-      </c>
-      <c r="P11" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>84</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>9</v>
-      </c>
-      <c r="T11">
-        <v>6</v>
-      </c>
-      <c r="U11">
-        <v>4</v>
-      </c>
-      <c r="V11" t="s">
-        <v>85</v>
-      </c>
-      <c r="W11">
-        <v>0.205</v>
-      </c>
-      <c r="X11">
-        <v>0.362</v>
-      </c>
-      <c r="Y11">
-        <v>-0.233</v>
-      </c>
-      <c r="Z11">
-        <v>-18.065</v>
-      </c>
-      <c r="AA11">
-        <v>-101.5</v>
-      </c>
-      <c r="AB11">
-        <v>149.519</v>
-      </c>
-      <c r="AC11">
-        <v>46.4</v>
-      </c>
-      <c r="AD11">
-        <v>62</v>
-      </c>
-      <c r="AE11">
-        <v>3000</v>
-      </c>
-      <c r="AF11">
-        <v>5000</v>
-      </c>
-      <c r="AG11">
-        <v>1</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI11">
-        <v>150</v>
-      </c>
-      <c r="AJ11">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36">
-      <c r="B12">
-        <v>50008</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12">
-        <v>7</v>
-      </c>
-      <c r="E12">
-        <v>300</v>
-      </c>
-      <c r="F12">
-        <v>8</v>
-      </c>
-      <c r="G12">
-        <v>2000</v>
-      </c>
-      <c r="H12">
-        <v>8</v>
-      </c>
-      <c r="I12">
-        <v>4000</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>5</v>
-      </c>
-      <c r="N12" t="s">
-        <v>99</v>
-      </c>
-      <c r="O12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>84</v>
-      </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12">
-        <v>9</v>
-      </c>
-      <c r="T12">
-        <v>6</v>
-      </c>
-      <c r="U12">
-        <v>4</v>
-      </c>
-      <c r="V12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W12">
-        <v>0.205</v>
-      </c>
-      <c r="X12">
-        <v>0.362</v>
-      </c>
-      <c r="Y12">
-        <v>-0.233</v>
-      </c>
-      <c r="Z12">
-        <v>-18.065</v>
-      </c>
-      <c r="AA12">
-        <v>-101.5</v>
-      </c>
-      <c r="AB12">
-        <v>149.519</v>
-      </c>
-      <c r="AC12">
-        <v>46.4</v>
-      </c>
-      <c r="AD12">
-        <v>62</v>
-      </c>
-      <c r="AE12">
-        <v>3000</v>
-      </c>
-      <c r="AF12">
-        <v>5000</v>
-      </c>
-      <c r="AG12">
-        <v>1</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI12">
-        <v>150</v>
-      </c>
-      <c r="AJ12">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36">
-      <c r="B13">
-        <v>50009</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13">
-        <v>8</v>
-      </c>
-      <c r="E13">
-        <v>30</v>
-      </c>
-      <c r="F13">
-        <v>7</v>
-      </c>
-      <c r="G13">
-        <v>500</v>
-      </c>
-      <c r="H13">
-        <v>8</v>
-      </c>
-      <c r="I13">
-        <v>1000</v>
-      </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>2</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>101</v>
-      </c>
-      <c r="O13" t="s">
-        <v>82</v>
-      </c>
-      <c r="P13" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>84</v>
-      </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
-      <c r="S13">
-        <v>9</v>
-      </c>
-      <c r="T13">
-        <v>6</v>
-      </c>
-      <c r="U13">
-        <v>4</v>
-      </c>
-      <c r="V13" t="s">
-        <v>85</v>
-      </c>
-      <c r="W13">
-        <v>0.205</v>
-      </c>
-      <c r="X13">
-        <v>0.362</v>
-      </c>
-      <c r="Y13">
-        <v>-0.233</v>
-      </c>
-      <c r="Z13">
-        <v>-18.065</v>
-      </c>
-      <c r="AA13">
-        <v>-101.5</v>
-      </c>
-      <c r="AB13">
-        <v>149.519</v>
-      </c>
-      <c r="AC13">
-        <v>46.4</v>
-      </c>
-      <c r="AD13">
-        <v>42</v>
-      </c>
-      <c r="AE13">
-        <v>3000</v>
-      </c>
-      <c r="AF13">
-        <v>5000</v>
-      </c>
-      <c r="AG13">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI13">
-        <v>150</v>
-      </c>
-      <c r="AJ13">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36">
-      <c r="B14">
-        <v>50010</v>
-      </c>
-      <c r="C14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D14">
-        <v>9</v>
-      </c>
-      <c r="E14">
-        <v>40</v>
-      </c>
-      <c r="F14">
-        <v>9</v>
-      </c>
-      <c r="G14">
-        <v>400</v>
-      </c>
-      <c r="H14">
-        <v>6</v>
-      </c>
-      <c r="I14">
-        <v>4000</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>3</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>15</v>
-      </c>
-      <c r="N14" t="s">
-        <v>103</v>
-      </c>
-      <c r="O14" t="s">
-        <v>82</v>
-      </c>
-      <c r="P14" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>84</v>
-      </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
-      <c r="S14">
-        <v>9</v>
-      </c>
-      <c r="T14">
-        <v>6</v>
-      </c>
-      <c r="U14">
-        <v>4</v>
-      </c>
-      <c r="V14" t="s">
-        <v>85</v>
-      </c>
-      <c r="W14">
-        <v>0.205</v>
-      </c>
-      <c r="X14">
-        <v>0.362</v>
-      </c>
-      <c r="Y14">
-        <v>-0.233</v>
-      </c>
-      <c r="Z14">
-        <v>-18.065</v>
-      </c>
-      <c r="AA14">
-        <v>-101.5</v>
-      </c>
-      <c r="AB14">
-        <v>149.519</v>
-      </c>
-      <c r="AC14">
-        <v>46.4</v>
-      </c>
-      <c r="AD14">
-        <v>24</v>
-      </c>
-      <c r="AE14">
-        <v>3000</v>
-      </c>
-      <c r="AF14">
-        <v>5000</v>
-      </c>
-      <c r="AG14">
-        <v>1</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI14">
-        <v>150</v>
-      </c>
-      <c r="AJ14">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36">
-      <c r="B15">
-        <v>50011</v>
-      </c>
-      <c r="C15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15">
-        <v>10</v>
-      </c>
-      <c r="E15">
-        <v>10</v>
-      </c>
-      <c r="F15">
-        <v>6</v>
-      </c>
-      <c r="G15">
-        <v>100</v>
-      </c>
-      <c r="H15">
-        <v>15</v>
-      </c>
-      <c r="I15">
-        <v>1000</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>105</v>
-      </c>
-      <c r="O15" t="s">
-        <v>82</v>
-      </c>
-      <c r="P15" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>84</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="S15">
-        <v>9</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
-      </c>
-      <c r="U15">
-        <v>4</v>
-      </c>
-      <c r="V15" t="s">
-        <v>85</v>
-      </c>
-      <c r="W15">
-        <v>0.205</v>
-      </c>
-      <c r="X15">
-        <v>0.362</v>
-      </c>
-      <c r="Y15">
-        <v>-0.233</v>
-      </c>
-      <c r="Z15">
-        <v>-18.065</v>
-      </c>
-      <c r="AA15">
-        <v>-101.5</v>
-      </c>
-      <c r="AB15">
-        <v>149.519</v>
-      </c>
-      <c r="AC15">
-        <v>46.4</v>
-      </c>
-      <c r="AD15">
-        <v>80</v>
-      </c>
-      <c r="AE15">
-        <v>3000</v>
-      </c>
-      <c r="AF15">
-        <v>5000</v>
-      </c>
-      <c r="AG15">
-        <v>2</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI15">
-        <v>150</v>
-      </c>
-      <c r="AJ15">
+      <c r="AJ15" s="0">
         <v>150</v>
       </c>
     </row>
@@ -2881,4 +2917,9 @@
     <ignoredError sqref="A1:AJ3 A4:J4 L4:AJ4 A5:AJ15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>